--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9802-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9802-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{656166A8-B945-44F5-9FAC-D9AF3E2CB604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C32E6C9-75B7-4A03-900A-9AA927744773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C6ACDDAE-F862-4ECD-AD1F-30BD113E7AE6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B48F6823-0C5C-4EED-867D-E3FDB686E34B}"/>
   </bookViews>
   <sheets>
     <sheet name="9802-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1534,30 +1534,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EE7CE9-6F36-4559-89D5-59AC70AD7E93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF9F89E6-1D99-4C06-A31C-25C58824BE6E}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1747,7 +1747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1855,7 +1855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>29</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>29</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>29</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>29</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2020</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2019</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>2018</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="49">
         <v>2017</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="47">
         <v>2016</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="49">
         <v>2015</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>2014</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="49">
         <v>2013</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>2012</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="49">
         <v>2011</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>51</v>
       </c>
